--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación FONASA</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:53</t>
+    <t xml:space="preserve">2026-08-28 15:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:11</t>
+    <t xml:space="preserve">2026-08-29 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:47</t>
+    <t xml:space="preserve">2026-09-07 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:10</t>
+    <t xml:space="preserve">2026-09-08 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
